--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table87.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table87.xlsx
@@ -365,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -409,25 +409,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -871,261 +872,261 @@
       <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24" t="s">
+      <c r="D3" s="26"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="25"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24" t="s">
+      <c r="J3" s="26"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="25"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24" t="s">
+      <c r="M3" s="26"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24" t="s">
+      <c r="P3" s="26"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="S3" s="25"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24" t="s">
+      <c r="S3" s="26"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="V3" s="25"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24" t="s">
+      <c r="V3" s="26"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24" t="s">
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24" t="s">
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24" t="s">
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="24"/>
-      <c r="AJ3" s="24" t="s">
+      <c r="AH3" s="26"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="24"/>
-      <c r="AM3" s="24" t="s">
+      <c r="AK3" s="26"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="24"/>
-      <c r="AP3" s="24" t="s">
+      <c r="AN3" s="26"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="24"/>
-      <c r="AS3" s="24" t="s">
+      <c r="AQ3" s="26"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="24"/>
-      <c r="AV3" s="24" t="s">
+      <c r="AT3" s="26"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="24"/>
-      <c r="AY3" s="24" t="s">
+      <c r="AW3" s="26"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="24"/>
-      <c r="BB3" s="24" t="s">
+      <c r="AZ3" s="26"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="BC3" s="25"/>
+      <c r="BC3" s="26"/>
     </row>
     <row r="4" spans="1:55" ht="13" thickBot="1">
       <c r="A4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="L4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="N4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="O4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="27" t="s">
+      <c r="P4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="Q4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="26" t="s">
+      <c r="R4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="S4" s="27" t="s">
+      <c r="S4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="W4" s="26" t="s">
+      <c r="W4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="X4" s="26" t="s">
+      <c r="X4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="Y4" s="27" t="s">
+      <c r="Y4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="Z4" s="26" t="s">
+      <c r="Z4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" s="26" t="s">
+      <c r="AA4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AB4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AC4" s="26" t="s">
+      <c r="AC4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AD4" s="26" t="s">
+      <c r="AD4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AE4" s="27" t="s">
+      <c r="AE4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AF4" s="26" t="s">
+      <c r="AF4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AG4" s="26" t="s">
+      <c r="AG4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AH4" s="27" t="s">
+      <c r="AH4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AI4" s="26" t="s">
+      <c r="AI4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AJ4" s="26" t="s">
+      <c r="AJ4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="27" t="s">
+      <c r="AK4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AL4" s="26" t="s">
+      <c r="AL4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AM4" s="26" t="s">
+      <c r="AM4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AN4" s="27" t="s">
+      <c r="AN4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AO4" s="26" t="s">
+      <c r="AO4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AP4" s="26" t="s">
+      <c r="AP4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AQ4" s="27" t="s">
+      <c r="AQ4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AR4" s="26" t="s">
+      <c r="AR4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AS4" s="26" t="s">
+      <c r="AS4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AT4" s="27" t="s">
+      <c r="AT4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AU4" s="26" t="s">
+      <c r="AU4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AV4" s="26" t="s">
+      <c r="AV4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AW4" s="27" t="s">
+      <c r="AW4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AX4" s="26" t="s">
+      <c r="AX4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AY4" s="26" t="s">
+      <c r="AY4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AZ4" s="27" t="s">
+      <c r="AZ4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="BA4" s="26" t="s">
+      <c r="BA4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="BB4" s="26" t="s">
+      <c r="BB4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="BC4" s="27" t="s">
+      <c r="BC4" s="28" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1498,7 +1499,7 @@
       <c r="BB7" s="3"/>
       <c r="BC7" s="4"/>
     </row>
-    <row r="8" spans="1:55">
+    <row r="8" spans="1:55" s="24" customFormat="1">
       <c r="A8" s="21" t="s">
         <v>20</v>
       </c>
@@ -3107,7 +3108,7 @@
       <c r="BB18" s="3"/>
       <c r="BC18" s="4"/>
     </row>
-    <row r="19" spans="1:55">
+    <row r="19" spans="1:55" s="24" customFormat="1">
       <c r="A19" s="21" t="s">
         <v>20</v>
       </c>
